--- a/results/gmac_snr6dB/gmac_snr6dB_classB_Ru48_Rv48_SC/classB_Ru48_Rv48_snr6dB_SC.xlsx
+++ b/results/gmac_snr6dB/gmac_snr6dB_classB_Ru48_Rv48_SC/classB_Ru48_Rv48_snr6dB_SC.xlsx
@@ -494,7 +494,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gaussian MAC — Class B, (Ru=0.48, Rv=0.48), SNR=6dB, SC (L=1), pure_MC design</t>
+          <t>Gaussian MAC — Class B, (Ru=0.48, Rv=0.48), SNR=6dB, SC (L=1)</t>
         </is>
       </c>
     </row>
@@ -697,10 +697,10 @@
         <v>0.9609</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0048</v>
+        <v>0.0046</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="11">
@@ -723,10 +723,10 @@
         <v>0.9648</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0012</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="12">
@@ -749,10 +749,10 @@
         <v>0.9629</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0003333333333333333</v>
+        <v>0.0009</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="14">

--- a/results/gmac_snr6dB/gmac_snr6dB_classB_Ru48_Rv48_SC/classB_Ru48_Rv48_snr6dB_SC.xlsx
+++ b/results/gmac_snr6dB/gmac_snr6dB_classB_Ru48_Rv48_SC/classB_Ru48_Rv48_snr6dB_SC.xlsx
@@ -16,10 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,30 +30,15 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="13"/>
+      <sz val="12"/>
     </font>
     <font>
       <i val="1"/>
-      <color rgb="00555555"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <i val="1"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00888888"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <i val="1"/>
-      <color rgb="00888888"/>
     </font>
   </fonts>
   <fills count="3">
@@ -87,14 +73,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -104,13 +86,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -487,7 +463,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -566,7 +542,7 @@
       <c r="F5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="6" t="n">
         <v>0.07240000000000001</v>
       </c>
       <c r="H5" s="4" t="n">
@@ -592,7 +568,7 @@
       <c r="F6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="6" t="n">
         <v>0.0638</v>
       </c>
       <c r="H6" s="4" t="n">
@@ -616,9 +592,9 @@
         <v>0.4688</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="G7" s="5" t="n">
+        <v>0.9376</v>
+      </c>
+      <c r="G7" s="6" t="n">
         <v>0.0456</v>
       </c>
       <c r="H7" s="4" t="n">
@@ -644,7 +620,7 @@
       <c r="F8" s="5" t="n">
         <v>0.9688</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="6" t="n">
         <v>0.0246</v>
       </c>
       <c r="H8" s="4" t="n">
@@ -670,11 +646,11 @@
       <c r="F9" s="5" t="n">
         <v>0.9688</v>
       </c>
-      <c r="G9" s="5" t="n">
-        <v>0.0152</v>
+      <c r="G9" s="6" t="n">
+        <v>0.01585</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="10">
@@ -694,13 +670,13 @@
         <v>0.4805</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.9609</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>0.0046</v>
+        <v>0.961</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.004567</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>10000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="11">
@@ -722,11 +698,11 @@
       <c r="F11" s="5" t="n">
         <v>0.9648</v>
       </c>
-      <c r="G11" s="5" t="n">
-        <v>0.0012</v>
+      <c r="G11" s="6" t="n">
+        <v>0.00106</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="12">
@@ -746,34 +722,30 @@
         <v>0.4814</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.9629</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.9628</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.00102</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Capacity</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="8" t="n">
-        <v>0.688195269487774</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>0.688195269487774</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>1.376390538975548</v>
-      </c>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
+      <c r="D14" t="n">
+        <v>0.6882</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.6882</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.3764</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
